--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_repeat_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_repeat_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.8710416666666667</v>
+        <v>0.8642793987621573</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8672031485466749</v>
+        <v>0.9785591187473175</v>
       </c>
       <c r="C2" t="n">
-        <v>0.136341500066543</v>
+        <v>0.08959806004261171</v>
       </c>
       <c r="D2" t="n">
-        <v>2.056423594522536</v>
+        <v>0.2399737868620034</v>
       </c>
       <c r="E2" t="n">
-        <v>21.85672318921371</v>
+        <v>13.23642339716213</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7810416666666666</v>
+        <v>0.8381962864721486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.845842177535726</v>
+        <v>0.9769279926335221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3690115222961741</v>
+        <v>0.1243887586865748</v>
       </c>
       <c r="I2" t="n">
-        <v>2.899629993346782</v>
+        <v>0.5195427022274276</v>
       </c>
       <c r="J2" t="n">
-        <v>5.317524580648406</v>
+        <v>1.458504143849426</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9854166666666666</v>
+        <v>0.9973474801061007</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9837728937728938</v>
+        <v>0.9992337164750957</v>
       </c>
       <c r="M2" t="n">
-        <v>0.044</v>
+        <v>0.012</v>
       </c>
       <c r="N2" t="n">
-        <v>0.125971871228298</v>
+        <v>0.03365058335046304</v>
       </c>
       <c r="O2" t="n">
-        <v>8.954618432284352</v>
+        <v>2.643856176790469</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
